--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{134A9A12-56F1-4079-8E68-A8626E5472BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44924D10-1577-4E84-A7E7-E7A567A94CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0945ECDE-285D-43F0-9679-7CF33A803641}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CC876D83-447D-4ABA-8D1E-FB689D10F666}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3881,7 +3881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A939758-AAC6-4D5C-8131-1488C3E55468}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF83B10E-89AF-4A78-AE08-DFA6F523B703}">
   <dimension ref="B9:T224"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15939,7 +15939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50CD3DED-DA7A-4001-A5C5-242B1257DE76}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9F050A3-B85C-4BEC-912C-86E02CC8A671}">
   <dimension ref="B9:T563"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44924D10-1577-4E84-A7E7-E7A567A94CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03283FB0-5A1A-4573-957F-3312C15CDE15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CC876D83-447D-4ABA-8D1E-FB689D10F666}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CDAA8088-038A-439F-8454-45F6AC005662}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3881,7 +3881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF83B10E-89AF-4A78-AE08-DFA6F523B703}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F19286-5B41-451B-AF14-DEC77CCA67BA}">
   <dimension ref="B9:T224"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15939,7 +15939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9F050A3-B85C-4BEC-912C-86E02CC8A671}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7160095-161B-4116-A270-70EB7BC783CE}">
   <dimension ref="B9:T563"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03283FB0-5A1A-4573-957F-3312C15CDE15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4664B0D2-C851-4C3C-B308-6A53B3B034E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CDAA8088-038A-439F-8454-45F6AC005662}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{983501A8-04D4-4110-AA51-0EF4583205AB}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3881,7 +3881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F19286-5B41-451B-AF14-DEC77CCA67BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83718771-9300-40E3-B73B-A47454E957DA}">
   <dimension ref="B9:T224"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15939,7 +15939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7160095-161B-4116-A270-70EB7BC783CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6FE635B-AD23-46BA-BEFF-BAE981DBB7FF}">
   <dimension ref="B9:T563"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4664B0D2-C851-4C3C-B308-6A53B3B034E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9C78486-945E-43BD-9CBA-300E7DAFA216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{983501A8-04D4-4110-AA51-0EF4583205AB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8F700B95-715D-46AA-91BD-E3354529636A}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3881,7 +3881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83718771-9300-40E3-B73B-A47454E957DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74975EDC-2FCD-41BB-8B61-A702F507D309}">
   <dimension ref="B9:T224"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15939,7 +15939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6FE635B-AD23-46BA-BEFF-BAE981DBB7FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871355ED-5FA1-43E3-9E85-9D66447BE56D}">
   <dimension ref="B9:T563"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41565,7 +41565,7 @@
         <v>33</v>
       </c>
       <c r="L516">
-        <v>0.2194967333865103</v>
+        <v>0.21949673338651032</v>
       </c>
     </row>
     <row r="517" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9C78486-945E-43BD-9CBA-300E7DAFA216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{560E5392-A422-4FAD-A124-9B5B6EF5947A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8F700B95-715D-46AA-91BD-E3354529636A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A750B573-A944-442C-A3DD-40007DEEACB7}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1422,15 +1422,18 @@
     <t>ep_solar_pv_G100000810010</t>
   </si>
   <si>
+    <t>ep_windon_wind_BRA</t>
+  </si>
+  <si>
+    <t>windon</t>
+  </si>
+  <si>
+    <t>elc_won-BRA</t>
+  </si>
+  <si>
     <t>ep_windon_wind_G100000906283</t>
   </si>
   <si>
-    <t>windon</t>
-  </si>
-  <si>
-    <t>elc_won-BRA</t>
-  </si>
-  <si>
     <t>ep_windon_wind_G100000906294</t>
   </si>
   <si>
@@ -1441,9 +1444,6 @@
   </si>
   <si>
     <t>ep_windon_wind_G100000926950</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_c_won-BRA</t>
   </si>
   <si>
     <t>~fi_process</t>
@@ -3881,7 +3881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74975EDC-2FCD-41BB-8B61-A702F507D309}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF6A274F-FCF1-437C-A400-F6416B4F98E8}">
   <dimension ref="B9:T224"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15939,7 +15939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871355ED-5FA1-43E3-9E85-9D66447BE56D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C92AA537-0F5E-4E18-901F-FC63D86F8342}">
   <dimension ref="B9:T563"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39365,7 +39365,7 @@
         <v>461</v>
       </c>
       <c r="P451" t="s">
-        <v>821</v>
+        <v>477</v>
       </c>
       <c r="Q451" t="s">
         <v>478</v>
@@ -39377,7 +39377,7 @@
         <v>817</v>
       </c>
       <c r="T451" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="452" spans="2:20" x14ac:dyDescent="0.45">
@@ -39418,7 +39418,7 @@
         <v>464</v>
       </c>
       <c r="P452" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="Q452" t="s">
         <v>478</v>
@@ -39471,7 +39471,7 @@
         <v>465</v>
       </c>
       <c r="P453" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="Q453" t="s">
         <v>478</v>
@@ -39524,7 +39524,7 @@
         <v>466</v>
       </c>
       <c r="P454" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="Q454" t="s">
         <v>478</v>
@@ -39577,7 +39577,7 @@
         <v>467</v>
       </c>
       <c r="P455" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="Q455" t="s">
         <v>478</v>
@@ -39630,7 +39630,7 @@
         <v>468</v>
       </c>
       <c r="P456" t="s">
-        <v>477</v>
+        <v>825</v>
       </c>
       <c r="Q456" t="s">
         <v>478</v>
@@ -39642,7 +39642,7 @@
         <v>817</v>
       </c>
       <c r="T456" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="457" spans="2:20" x14ac:dyDescent="0.45">
@@ -41565,7 +41565,7 @@
         <v>33</v>
       </c>
       <c r="L516">
-        <v>0.21949673338651032</v>
+        <v>0.22262148291261796</v>
       </c>
     </row>
     <row r="517" spans="2:12" x14ac:dyDescent="0.45">
@@ -41600,7 +41600,7 @@
         <v>44</v>
       </c>
       <c r="L517">
-        <v>0.22379959893442622</v>
+        <v>0.22513165750609462</v>
       </c>
     </row>
     <row r="518" spans="2:12" x14ac:dyDescent="0.45">
@@ -41635,7 +41635,7 @@
         <v>42</v>
       </c>
       <c r="L518">
-        <v>0.18644117299999999</v>
+        <v>0.19644130759920511</v>
       </c>
     </row>
     <row r="519" spans="2:12" x14ac:dyDescent="0.45">
@@ -41670,7 +41670,7 @@
         <v>41</v>
       </c>
       <c r="L519">
-        <v>0.21518521773913046</v>
+        <v>0.21832116900311777</v>
       </c>
     </row>
     <row r="520" spans="2:12" x14ac:dyDescent="0.45">
@@ -41705,7 +41705,7 @@
         <v>40</v>
       </c>
       <c r="L520">
-        <v>0.21726942388291598</v>
+        <v>0.22177733168413233</v>
       </c>
     </row>
     <row r="521" spans="2:12" x14ac:dyDescent="0.45">
@@ -41740,7 +41740,7 @@
         <v>39</v>
       </c>
       <c r="L521">
-        <v>0.23258579800000001</v>
+        <v>0.24434982557087589</v>
       </c>
     </row>
     <row r="522" spans="2:12" x14ac:dyDescent="0.45">
@@ -41775,7 +41775,7 @@
         <v>38</v>
       </c>
       <c r="L522">
-        <v>0.22404021879443609</v>
+        <v>0.22552124590227043</v>
       </c>
     </row>
     <row r="523" spans="2:12" x14ac:dyDescent="0.45">
@@ -41810,7 +41810,7 @@
         <v>37</v>
       </c>
       <c r="L523">
-        <v>0.21947491535932162</v>
+        <v>0.22248956814466347</v>
       </c>
     </row>
     <row r="524" spans="2:12" x14ac:dyDescent="0.45">
@@ -41845,7 +41845,7 @@
         <v>36</v>
       </c>
       <c r="L524">
-        <v>0.21402153039449665</v>
+        <v>0.21586608384990219</v>
       </c>
     </row>
     <row r="525" spans="2:12" x14ac:dyDescent="0.45">
@@ -41880,7 +41880,7 @@
         <v>35</v>
       </c>
       <c r="L525">
-        <v>0.22166276703901272</v>
+        <v>0.22289265249516904</v>
       </c>
     </row>
     <row r="526" spans="2:12" x14ac:dyDescent="0.45">
@@ -41915,7 +41915,7 @@
         <v>34</v>
       </c>
       <c r="L526">
-        <v>0.2193191867463678</v>
+        <v>0.22234577966477387</v>
       </c>
     </row>
     <row r="527" spans="2:12" x14ac:dyDescent="0.45">
@@ -41950,7 +41950,7 @@
         <v>33</v>
       </c>
       <c r="L527">
-        <v>0.21962561388788424</v>
+        <v>0.22037217171570839</v>
       </c>
     </row>
     <row r="528" spans="2:12" x14ac:dyDescent="0.45">
@@ -41985,7 +41985,7 @@
         <v>32</v>
       </c>
       <c r="L528">
-        <v>0.21567659264467118</v>
+        <v>0.21792713326969154</v>
       </c>
     </row>
     <row r="529" spans="2:12" x14ac:dyDescent="0.45">
@@ -42020,7 +42020,7 @@
         <v>31</v>
       </c>
       <c r="L529">
-        <v>0.2181106326581552</v>
+        <v>0.21944498997094997</v>
       </c>
     </row>
     <row r="530" spans="2:12" x14ac:dyDescent="0.45">
@@ -42055,7 +42055,7 @@
         <v>30</v>
       </c>
       <c r="L530">
-        <v>0.21427342813517564</v>
+        <v>0.21515603199733352</v>
       </c>
     </row>
     <row r="531" spans="2:12" x14ac:dyDescent="0.45">
@@ -42090,7 +42090,7 @@
         <v>30</v>
       </c>
       <c r="L531">
-        <v>0.22512320074119188</v>
+        <v>0.22692412387946517</v>
       </c>
     </row>
     <row r="532" spans="2:12" x14ac:dyDescent="0.45">
@@ -42125,7 +42125,7 @@
         <v>32</v>
       </c>
       <c r="L532">
-        <v>0.23244104500000001</v>
+        <v>0.23244104508238642</v>
       </c>
     </row>
     <row r="533" spans="2:12" x14ac:dyDescent="0.45">
@@ -42160,7 +42160,7 @@
         <v>33</v>
       </c>
       <c r="L533">
-        <v>0.22594542899999998</v>
+        <v>0.22989228754569199</v>
       </c>
     </row>
     <row r="534" spans="2:12" x14ac:dyDescent="0.45">
@@ -42195,7 +42195,7 @@
         <v>32</v>
       </c>
       <c r="L534">
-        <v>0.225945429</v>
+        <v>0.22989228754569199</v>
       </c>
     </row>
     <row r="535" spans="2:12" x14ac:dyDescent="0.45">
@@ -42209,21 +42209,21 @@
         <v>463</v>
       </c>
       <c r="E535">
-        <v>2024</v>
+        <v>1998</v>
       </c>
       <c r="F535">
-        <v>0.36</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G535">
         <v>0.33123000000000002</v>
       </c>
       <c r="L535">
-        <v>0.31836624099999999</v>
+        <v>0.5645739708666484</v>
       </c>
     </row>
     <row r="536" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B536" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C536" t="s">
         <v>462</v>
@@ -42232,21 +42232,21 @@
         <v>463</v>
       </c>
       <c r="E536">
-        <v>2024</v>
+        <v>1999</v>
       </c>
       <c r="F536">
-        <v>0.42</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="G536">
         <v>0.33123000000000002</v>
       </c>
       <c r="L536">
-        <v>0.22148911199999999</v>
+        <v>0.45332012041347369</v>
       </c>
     </row>
     <row r="537" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B537" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C537" t="s">
         <v>462</v>
@@ -42255,21 +42255,21 @@
         <v>463</v>
       </c>
       <c r="E537">
-        <v>2028</v>
+        <v>2004</v>
       </c>
       <c r="F537">
-        <v>0.39600000000000002</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="G537">
-        <v>0.33122999999999997</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L537">
-        <v>0.42627854799999998</v>
+        <v>0.23618573857372882</v>
       </c>
     </row>
     <row r="538" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B538" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C538" t="s">
         <v>462</v>
@@ -42278,21 +42278,21 @@
         <v>463</v>
       </c>
       <c r="E538">
-        <v>2020</v>
+        <v>2006</v>
       </c>
       <c r="F538">
-        <v>0.2016</v>
+        <v>0.20830000000000001</v>
       </c>
       <c r="G538">
-        <v>0.33123000000000002</v>
+        <v>0.33122999999999997</v>
       </c>
       <c r="L538">
-        <v>0.27049498300000002</v>
+        <v>0.51672265032050479</v>
       </c>
     </row>
     <row r="539" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B539" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C539" t="s">
         <v>462</v>
@@ -42301,21 +42301,21 @@
         <v>463</v>
       </c>
       <c r="E539">
-        <v>2024</v>
+        <v>2007</v>
       </c>
       <c r="F539">
-        <v>0.248</v>
+        <v>1.0199999999999999E-2</v>
       </c>
       <c r="G539">
         <v>0.33123000000000002</v>
       </c>
       <c r="L539">
-        <v>0.47013602999999998</v>
+        <v>0.49916874320810006</v>
       </c>
     </row>
     <row r="540" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B540" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C540" t="s">
         <v>462</v>
@@ -42324,21 +42324,21 @@
         <v>463</v>
       </c>
       <c r="E540">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="F540">
-        <v>5.0000000000000001E-3</v>
+        <v>9.5799999999999996E-2</v>
       </c>
       <c r="G540">
         <v>0.33123000000000002</v>
       </c>
       <c r="L540">
-        <v>0.35894824600000003</v>
+        <v>0.54767704593820998</v>
       </c>
     </row>
     <row r="541" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B541" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C541" t="s">
         <v>462</v>
@@ -42347,21 +42347,21 @@
         <v>463</v>
       </c>
       <c r="E541">
-        <v>1999</v>
+        <v>2009</v>
       </c>
       <c r="F541">
-        <v>1.2500000000000001E-2</v>
+        <v>0.26480000000000015</v>
       </c>
       <c r="G541">
         <v>0.33123000000000002</v>
       </c>
       <c r="L541">
-        <v>0.4412179054</v>
+        <v>0.55129966168958344</v>
       </c>
     </row>
     <row r="542" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B542" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C542" t="s">
         <v>462</v>
@@ -42370,21 +42370,21 @@
         <v>463</v>
       </c>
       <c r="E542">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="F542">
-        <v>4.7999999999999996E-3</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="G542">
-        <v>0.33123000000000002</v>
+        <v>0.33122999999999991</v>
       </c>
       <c r="L542">
-        <v>0.20931881999999999</v>
+        <v>0.55911401279835415</v>
       </c>
     </row>
     <row r="543" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B543" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C543" t="s">
         <v>462</v>
@@ -42393,21 +42393,21 @@
         <v>463</v>
       </c>
       <c r="E543">
-        <v>2006</v>
+        <v>2011</v>
       </c>
       <c r="F543">
-        <v>0.20830000000000001</v>
+        <v>0.37269999999999998</v>
       </c>
       <c r="G543">
-        <v>0.33122999999999997</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L543">
-        <v>0.35039227405328849</v>
+        <v>0.43634226558127542</v>
       </c>
     </row>
     <row r="544" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B544" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C544" t="s">
         <v>462</v>
@@ -42416,21 +42416,21 @@
         <v>463</v>
       </c>
       <c r="E544">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="F544">
-        <v>1.0199999999999999E-2</v>
+        <v>0.59730000000000005</v>
       </c>
       <c r="G544">
-        <v>0.33123000000000002</v>
+        <v>0.33122999999999997</v>
       </c>
       <c r="L544">
-        <v>0.499168746</v>
+        <v>0.4176634112529819</v>
       </c>
     </row>
     <row r="545" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B545" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C545" t="s">
         <v>462</v>
@@ -42439,21 +42439,21 @@
         <v>463</v>
       </c>
       <c r="E545">
-        <v>2008</v>
+        <v>2013</v>
       </c>
       <c r="F545">
-        <v>9.5799999999999996E-2</v>
+        <v>0.35060000000000002</v>
       </c>
       <c r="G545">
-        <v>0.33123000000000002</v>
+        <v>0.33122999999999997</v>
       </c>
       <c r="L545">
-        <v>0.50977305209081425</v>
+        <v>0.50664803244978052</v>
       </c>
     </row>
     <row r="546" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B546" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C546" t="s">
         <v>462</v>
@@ -42462,21 +42462,21 @@
         <v>463</v>
       </c>
       <c r="E546">
-        <v>2009</v>
+        <v>2014</v>
       </c>
       <c r="F546">
-        <v>0.26480000000000015</v>
+        <v>2.7781000000000002</v>
       </c>
       <c r="G546">
-        <v>0.33123000000000002</v>
+        <v>0.33123000000000025</v>
       </c>
       <c r="L546">
-        <v>0.47897395288746214</v>
+        <v>0.56350748949957941</v>
       </c>
     </row>
     <row r="547" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B547" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C547" t="s">
         <v>462</v>
@@ -42485,21 +42485,21 @@
         <v>463</v>
       </c>
       <c r="E547">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="F547">
-        <v>0.32700000000000001</v>
+        <v>2.8485000000000014</v>
       </c>
       <c r="G547">
-        <v>0.33122999999999991</v>
+        <v>0.33123000000000008</v>
       </c>
       <c r="L547">
-        <v>0.52394352041253811</v>
+        <v>0.42442445788263505</v>
       </c>
     </row>
     <row r="548" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B548" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C548" t="s">
         <v>462</v>
@@ -42508,21 +42508,21 @@
         <v>463</v>
       </c>
       <c r="E548">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="F548">
-        <v>0.37269999999999998</v>
+        <v>2.6350000000000011</v>
       </c>
       <c r="G548">
-        <v>0.33123000000000002</v>
+        <v>0.33122999999999997</v>
       </c>
       <c r="L548">
-        <v>0.38604758353367324</v>
+        <v>0.4328694738035278</v>
       </c>
     </row>
     <row r="549" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B549" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C549" t="s">
         <v>462</v>
@@ -42531,21 +42531,21 @@
         <v>463</v>
       </c>
       <c r="E549">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="F549">
-        <v>0.59730000000000005</v>
+        <v>2.1047000000000002</v>
       </c>
       <c r="G549">
-        <v>0.33122999999999997</v>
+        <v>0.33123000000000014</v>
       </c>
       <c r="L549">
-        <v>0.37494612763167584</v>
+        <v>0.43091264437815563</v>
       </c>
     </row>
     <row r="550" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B550" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C550" t="s">
         <v>462</v>
@@ -42554,21 +42554,21 @@
         <v>463</v>
       </c>
       <c r="E550">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="F550">
-        <v>0.35060000000000002</v>
+        <v>2.0630000000000006</v>
       </c>
       <c r="G550">
-        <v>0.33122999999999997</v>
+        <v>0.33123000000000014</v>
       </c>
       <c r="L550">
-        <v>0.41330607225470622</v>
+        <v>0.40279448081237212</v>
       </c>
     </row>
     <row r="551" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B551" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C551" t="s">
         <v>462</v>
@@ -42577,21 +42577,21 @@
         <v>463</v>
       </c>
       <c r="E551">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="F551">
-        <v>2.7781000000000002</v>
+        <v>0.97260000000000002</v>
       </c>
       <c r="G551">
-        <v>0.33123000000000025</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L551">
-        <v>0.47719589194672596</v>
+        <v>0.45135038057700744</v>
       </c>
     </row>
     <row r="552" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B552" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C552" t="s">
         <v>462</v>
@@ -42600,21 +42600,21 @@
         <v>463</v>
       </c>
       <c r="E552">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="F552">
-        <v>2.8485000000000014</v>
+        <v>1.7780999999999998</v>
       </c>
       <c r="G552">
-        <v>0.33123000000000008</v>
+        <v>0.33122999999999997</v>
       </c>
       <c r="L552">
-        <v>0.39291140159136373</v>
+        <v>0.48312575418447107</v>
       </c>
     </row>
     <row r="553" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B553" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C553" t="s">
         <v>462</v>
@@ -42623,21 +42623,21 @@
         <v>463</v>
       </c>
       <c r="E553">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="F553">
-        <v>2.6350000000000011</v>
+        <v>3.6783999999999977</v>
       </c>
       <c r="G553">
-        <v>0.33122999999999997</v>
+        <v>0.33123000000000025</v>
       </c>
       <c r="L553">
-        <v>0.38951181748250491</v>
+        <v>0.47956460471850842</v>
       </c>
     </row>
     <row r="554" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B554" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C554" t="s">
         <v>462</v>
@@ -42646,21 +42646,21 @@
         <v>463</v>
       </c>
       <c r="E554">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="F554">
-        <v>2.1047000000000002</v>
+        <v>2.8867349999999652</v>
       </c>
       <c r="G554">
-        <v>0.33123000000000014</v>
+        <v>0.33122999999999986</v>
       </c>
       <c r="L554">
-        <v>0.40119191815959537</v>
+        <v>0.39515557852336064</v>
       </c>
     </row>
     <row r="555" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B555" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C555" t="s">
         <v>462</v>
@@ -42669,21 +42669,21 @@
         <v>463</v>
       </c>
       <c r="E555">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="F555">
-        <v>2.0630000000000006</v>
+        <v>5.3633000000000015</v>
       </c>
       <c r="G555">
-        <v>0.33123000000000014</v>
+        <v>0.3312299999999998</v>
       </c>
       <c r="L555">
-        <v>0.36916534520339322</v>
+        <v>0.41490439735357182</v>
       </c>
     </row>
     <row r="556" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B556" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C556" t="s">
         <v>462</v>
@@ -42692,21 +42692,21 @@
         <v>463</v>
       </c>
       <c r="E556">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="F556">
-        <v>0.97260000000000002</v>
+        <v>3.5614999999999997</v>
       </c>
       <c r="G556">
-        <v>0.33123000000000002</v>
+        <v>0.33123000000000014</v>
       </c>
       <c r="L556">
-        <v>0.43006369324470495</v>
+        <v>0.3520443623969331</v>
       </c>
     </row>
     <row r="557" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B557" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C557" t="s">
         <v>462</v>
@@ -42715,21 +42715,21 @@
         <v>463</v>
       </c>
       <c r="E557">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="F557">
-        <v>1.7780999999999998</v>
+        <v>0.40590000000000004</v>
       </c>
       <c r="G557">
         <v>0.33122999999999997</v>
       </c>
       <c r="L557">
-        <v>0.44649955012372777</v>
+        <v>0.32845670610349081</v>
       </c>
     </row>
     <row r="558" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B558" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C558" t="s">
         <v>462</v>
@@ -42738,21 +42738,21 @@
         <v>463</v>
       </c>
       <c r="E558">
-        <v>2021</v>
+        <v>2028</v>
       </c>
       <c r="F558">
-        <v>3.6783999999999977</v>
+        <v>2.1988000000000003</v>
       </c>
       <c r="G558">
-        <v>0.33123000000000025</v>
+        <v>0.33122999999999991</v>
       </c>
       <c r="L558">
-        <v>0.44326003344856485</v>
+        <v>0.38556613642052773</v>
       </c>
     </row>
     <row r="559" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B559" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C559" t="s">
         <v>462</v>
@@ -42761,21 +42761,21 @@
         <v>463</v>
       </c>
       <c r="E559">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F559">
-        <v>2.8867349999999652</v>
+        <v>0.36</v>
       </c>
       <c r="G559">
-        <v>0.33122999999999986</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L559">
-        <v>0.35636048205488646</v>
+        <v>0.33076167590529609</v>
       </c>
     </row>
     <row r="560" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B560" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C560" t="s">
         <v>462</v>
@@ -42784,21 +42784,21 @@
         <v>463</v>
       </c>
       <c r="E560">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F560">
-        <v>5.3633000000000015</v>
+        <v>0.42</v>
       </c>
       <c r="G560">
-        <v>0.3312299999999998</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L560">
-        <v>0.37942092565019675</v>
+        <v>0.22148911105282351</v>
       </c>
     </row>
     <row r="561" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B561" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C561" t="s">
         <v>462</v>
@@ -42807,21 +42807,21 @@
         <v>463</v>
       </c>
       <c r="E561">
-        <v>2024</v>
+        <v>2028</v>
       </c>
       <c r="F561">
-        <v>3.5614999999999997</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="G561">
-        <v>0.33123000000000014</v>
+        <v>0.33122999999999997</v>
       </c>
       <c r="L561">
-        <v>0.33278249955880956</v>
+        <v>0.42745274933005312</v>
       </c>
     </row>
     <row r="562" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B562" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C562" t="s">
         <v>462</v>
@@ -42830,16 +42830,16 @@
         <v>463</v>
       </c>
       <c r="E562">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="F562">
-        <v>0.40590000000000004</v>
+        <v>0.2016</v>
       </c>
       <c r="G562">
-        <v>0.33122999999999997</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L562">
-        <v>0.32263620657945302</v>
+        <v>0.27049500804172472</v>
       </c>
     </row>
     <row r="563" spans="2:12" x14ac:dyDescent="0.45">
@@ -42853,16 +42853,16 @@
         <v>463</v>
       </c>
       <c r="E563">
-        <v>2028</v>
+        <v>2024</v>
       </c>
       <c r="F563">
-        <v>2.1988000000000003</v>
+        <v>0.248</v>
       </c>
       <c r="G563">
-        <v>0.33122999999999991</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L563">
-        <v>0.37823190691554487</v>
+        <v>0.47013602646504421</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{560E5392-A422-4FAD-A124-9B5B6EF5947A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB24797C-FA2B-47BC-9A0D-E5373F8911BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A750B573-A944-442C-A3DD-40007DEEACB7}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9AB87553-0D1B-4D71-82E9-5BDBE627DD87}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3881,7 +3881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF6A274F-FCF1-437C-A400-F6416B4F98E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12DD3433-05C0-4519-BA60-D5C3598E14D7}">
   <dimension ref="B9:T224"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15939,7 +15939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C92AA537-0F5E-4E18-901F-FC63D86F8342}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D989B0B-573E-4AA0-8309-187387F97D13}">
   <dimension ref="B9:T563"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB24797C-FA2B-47BC-9A0D-E5373F8911BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{09485C12-CE5D-45FE-8780-408B72147DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9AB87553-0D1B-4D71-82E9-5BDBE627DD87}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A444CE57-4EF2-46F1-9DB5-F625C34D6E0C}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3881,7 +3881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12DD3433-05C0-4519-BA60-D5C3598E14D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9C5061-01C2-43B5-914E-ADAC18E104A2}">
   <dimension ref="B9:T224"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15939,7 +15939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D989B0B-573E-4AA0-8309-187387F97D13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCEAC14E-910F-4FEE-B8CE-3E29DEA9F705}">
   <dimension ref="B9:T563"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09485C12-CE5D-45FE-8780-408B72147DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C3560D3-0717-4BF0-8271-5F86DC151978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A444CE57-4EF2-46F1-9DB5-F625C34D6E0C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D093386F-A446-4A9D-B6B1-4A6F42C6F5EB}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3881,7 +3881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9C5061-01C2-43B5-914E-ADAC18E104A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4706B9C4-5A39-4196-9838-2F8A0ED33879}">
   <dimension ref="B9:T224"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15939,7 +15939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCEAC14E-910F-4FEE-B8CE-3E29DEA9F705}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7955E2F4-14A1-44AE-A48D-BE84C4FB4391}">
   <dimension ref="B9:T563"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C3560D3-0717-4BF0-8271-5F86DC151978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{00CDCF13-0DF3-4295-ACBD-863B12F36D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D093386F-A446-4A9D-B6B1-4A6F42C6F5EB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FD8053FD-96A2-4613-B989-5965652AEBEF}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3881,7 +3881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4706B9C4-5A39-4196-9838-2F8A0ED33879}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0D53A38-6BA8-47F9-9FAC-D25AF440317B}">
   <dimension ref="B9:T224"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15939,7 +15939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7955E2F4-14A1-44AE-A48D-BE84C4FB4391}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B877594-4202-4202-9F3C-6D56E97602BD}">
   <dimension ref="B9:T563"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00CDCF13-0DF3-4295-ACBD-863B12F36D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{687AFC66-1A0D-4539-8A0F-022858023AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FD8053FD-96A2-4613-B989-5965652AEBEF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5931B26F-EFD4-4BDD-B560-2037AFB16F9B}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3881,7 +3881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0D53A38-6BA8-47F9-9FAC-D25AF440317B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7727247F-96E6-4888-B587-FDE2FBE0E51D}">
   <dimension ref="B9:T224"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15939,7 +15939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B877594-4202-4202-9F3C-6D56E97602BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87D8311-6C21-4084-B2D3-A348662C24AC}">
   <dimension ref="B9:T563"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{687AFC66-1A0D-4539-8A0F-022858023AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{170A2375-9EC3-450E-B83A-08B112748E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5931B26F-EFD4-4BDD-B560-2037AFB16F9B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B5677880-F989-4D1C-A749-9180EA9654E6}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3881,7 +3881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7727247F-96E6-4888-B587-FDE2FBE0E51D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BE3BCC6-1235-4CF6-BCEE-786A78EC6E45}">
   <dimension ref="B9:T224"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15939,7 +15939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87D8311-6C21-4084-B2D3-A348662C24AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8606C787-0681-497B-BC90-96A6DE958770}">
   <dimension ref="B9:T563"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{170A2375-9EC3-450E-B83A-08B112748E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBFA89D7-8487-4CD8-8068-5B4714040708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B5677880-F989-4D1C-A749-9180EA9654E6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FE1EF14D-BAC4-4778-A44B-FBC4D3720BCD}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3881,7 +3881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BE3BCC6-1235-4CF6-BCEE-786A78EC6E45}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E335E563-B4B9-455E-87BD-FE01B36B15C6}">
   <dimension ref="B9:T224"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15939,7 +15939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8606C787-0681-497B-BC90-96A6DE958770}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{603EDE88-C56C-4CF2-89A8-C3FD3E02F88E}">
   <dimension ref="B9:T563"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBFA89D7-8487-4CD8-8068-5B4714040708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29F7760D-7A49-4447-B47B-33439BEBBA32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FE1EF14D-BAC4-4778-A44B-FBC4D3720BCD}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12682" xr2:uid="{A2C79721-5585-40B2-A0E9-3991956D2FCD}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3881,7 +3881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E335E563-B4B9-455E-87BD-FE01B36B15C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FA8709D-0517-43BB-9646-BC78F8FE9201}">
   <dimension ref="B9:T224"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15939,7 +15939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{603EDE88-C56C-4CF2-89A8-C3FD3E02F88E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC1820F8-BAF2-42B5-B8BC-6226BFEF6DE0}">
   <dimension ref="B9:T563"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78303950-C122-43EB-9855-5355F7AA356E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8F13269-83F5-4DB2-A463-F3E2A93AE5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{23174164-C634-4D1D-8307-16A1764362EA}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EF2E2FE2-AB44-4C3E-99F4-CD54766DFD78}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3299,7 +3299,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{876D086F-EC16-4BE5-AABD-60B7F40290C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68CF99D8-D2CE-41AF-986A-E80E29C5CC3C}">
   <dimension ref="B9:T126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9869,7 +9869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82A47B38-6D94-4FED-A1E4-4FD981F5801F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECDBBCE2-D7BB-42CA-9F1D-903A82EFFC81}">
   <dimension ref="B9:T465"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -30301,7 +30301,7 @@
         <v>33</v>
       </c>
       <c r="L418">
-        <v>0.22262148291261796</v>
+        <v>0.22262148291261802</v>
       </c>
     </row>
     <row r="419" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8F13269-83F5-4DB2-A463-F3E2A93AE5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C387047A-B03D-4048-A82C-4A1E16D6FE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EF2E2FE2-AB44-4C3E-99F4-CD54766DFD78}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{56FFED8E-9981-48D3-A749-DC0968ED77CD}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3299,7 +3299,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68CF99D8-D2CE-41AF-986A-E80E29C5CC3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66FCDB26-30E7-4EEA-8F3D-F9C1A2214D94}">
   <dimension ref="B9:T126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9869,7 +9869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECDBBCE2-D7BB-42CA-9F1D-903A82EFFC81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3B2CC40-C3BF-4D69-B4FA-420935F9FBBA}">
   <dimension ref="B9:T465"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -30301,7 +30301,7 @@
         <v>33</v>
       </c>
       <c r="L418">
-        <v>0.22262148291261802</v>
+        <v>0.22262148291261796</v>
       </c>
     </row>
     <row r="419" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C387047A-B03D-4048-A82C-4A1E16D6FE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB54F80A-E5C5-4F18-88E5-0EA752D5AFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{56FFED8E-9981-48D3-A749-DC0968ED77CD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0993F49E-044F-4082-A527-B47D27404AE8}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3299,7 +3299,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66FCDB26-30E7-4EEA-8F3D-F9C1A2214D94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE408509-2FE7-4D9C-92E8-93409DEE2B3A}">
   <dimension ref="B9:T126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9869,7 +9869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3B2CC40-C3BF-4D69-B4FA-420935F9FBBA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FCDA353-F888-4BD7-8502-2FB45A896911}">
   <dimension ref="B9:T465"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB54F80A-E5C5-4F18-88E5-0EA752D5AFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E2A70CF-3CF2-43A1-9186-08D43C50641E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0993F49E-044F-4082-A527-B47D27404AE8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AADF6C27-7F56-4E53-9A40-06FF17395442}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3299,7 +3299,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE408509-2FE7-4D9C-92E8-93409DEE2B3A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EEFAAF6-A292-4CE3-BB84-AB4EE4B94AF7}">
   <dimension ref="B9:T126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9869,7 +9869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FCDA353-F888-4BD7-8502-2FB45A896911}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{517CF419-D8A6-480B-B268-412CE5597038}">
   <dimension ref="B9:T465"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -30301,7 +30301,7 @@
         <v>33</v>
       </c>
       <c r="L418">
-        <v>0.22262148291261796</v>
+        <v>0.22262148291261802</v>
       </c>
     </row>
     <row r="419" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E2A70CF-3CF2-43A1-9186-08D43C50641E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6ACCDF9F-9326-4F87-BCBA-79BA5286E0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AADF6C27-7F56-4E53-9A40-06FF17395442}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1C2AF10A-F7B9-45F8-8940-C205BDFDD6BB}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3299,7 +3299,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EEFAAF6-A292-4CE3-BB84-AB4EE4B94AF7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B3C3B5B-9F81-4A45-92BF-509F802C9BFA}">
   <dimension ref="B9:T126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9869,7 +9869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{517CF419-D8A6-480B-B268-412CE5597038}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D20795D7-9620-4425-B595-422E438CC116}">
   <dimension ref="B9:T465"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -30301,7 +30301,7 @@
         <v>33</v>
       </c>
       <c r="L418">
-        <v>0.22262148291261802</v>
+        <v>0.22262148291261796</v>
       </c>
     </row>
     <row r="419" spans="2:12" x14ac:dyDescent="0.45">
